--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrLendSpecInfo.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14205" windowHeight="5985"/>
@@ -10,7 +10,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,10 +37,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>委托开始日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>已完成额度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -62,14 +57,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>委托金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>委托截止日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>利率%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -79,6 +66,26 @@
   </si>
   <si>
     <t>投资经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易场所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清算速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令开始日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令终止日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -89,7 +96,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#,##0.00000000000000_ "/>
     <numFmt numFmtId="177" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="180" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -149,11 +156,11 @@
     <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,7 +434,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -435,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
@@ -443,21 +450,20 @@
     <col min="3" max="3" width="25.125" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
     <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="11.375" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="54.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
-    <col min="11" max="11" width="12.875" customWidth="1"/>
-    <col min="12" max="12" width="47.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="23.75" customWidth="1"/>
+    <col min="6" max="8" width="11.375" customWidth="1"/>
+    <col min="9" max="9" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="12.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="14.25" customWidth="1"/>
+    <col min="13" max="13" width="12.875" customWidth="1"/>
+    <col min="14" max="14" width="17.25" style="5" customWidth="1"/>
+    <col min="15" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -466,40 +472,46 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
